--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6752-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6752-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F127B17F-B4A0-48AE-A806-DE139778444E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D08E828A-B716-4A18-9ADA-FD0BF11A3B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{1CF62301-977E-4E21-915A-CD6FE2F64926}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{661C959B-A855-4C7A-8091-3E616EBA6D89}"/>
   </bookViews>
   <sheets>
     <sheet name="6752-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1505,23 +1505,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE391A30-720E-462E-B387-0BA88E1073F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E41A983-CF4E-4A4D-88A4-1311FFE5F11A}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1555,7 +1553,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1591,7 +1589,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1643,7 +1641,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1711,7 +1709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1783,7 +1781,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="12" t="s">
@@ -1811,7 +1809,7 @@
       <c r="W6" s="44"/>
       <c r="X6" s="40"/>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="45">
         <v>2023</v>
       </c>
@@ -1883,7 +1881,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47"/>
       <c r="B8" s="48"/>
       <c r="C8" s="15" t="s">
@@ -1911,7 +1909,7 @@
       <c r="W8" s="54"/>
       <c r="X8" s="50"/>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2022</v>
       </c>
@@ -1983,7 +1981,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37"/>
       <c r="B10" s="38"/>
       <c r="C10" s="12" t="s">
@@ -2011,7 +2009,7 @@
       <c r="W10" s="44"/>
       <c r="X10" s="40"/>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="45">
         <v>2021</v>
       </c>
@@ -2083,7 +2081,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="47"/>
       <c r="B12" s="48"/>
       <c r="C12" s="15" t="s">
@@ -2111,7 +2109,7 @@
       <c r="W12" s="54"/>
       <c r="X12" s="50"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2020</v>
       </c>
@@ -2183,7 +2181,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37"/>
       <c r="B14" s="38"/>
       <c r="C14" s="12" t="s">
@@ -2211,7 +2209,7 @@
       <c r="W14" s="44"/>
       <c r="X14" s="40"/>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="55">
         <v>2019</v>
       </c>
@@ -2283,7 +2281,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="57" t="s">
         <v>39</v>
       </c>
